--- a/_단기투자_INPUT.xlsx
+++ b/_단기투자_INPUT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6956B4-624E-4F22-8E23-2C6C8B0C4941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF7B052-B1D4-4FE7-85EA-F8A56E39831F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,11 +171,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="[Red]\▲#,##0;[Blue]\▼##,#00"/>
-    <numFmt numFmtId="180" formatCode="[Red]0.00%;[Blue]\-0.00%;0"/>
-    <numFmt numFmtId="182" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="183" formatCode="\+#,##0;\-#,##0;0"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="[Red]\▲#,##0;[Blue]\▼##,#00"/>
+    <numFmt numFmtId="178" formatCode="[Red]0.00%;[Blue]\-0.00%;0"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="180" formatCode="\+#,##0;\-#,##0;0"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -664,7 +664,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
@@ -676,10 +676,10 @@
     <xf numFmtId="41" fontId="5" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="4" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="6" fillId="4" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -688,7 +688,7 @@
     <xf numFmtId="41" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -700,7 +700,7 @@
     <xf numFmtId="41" fontId="3" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -709,7 +709,7 @@
     <xf numFmtId="41" fontId="3" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="6" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
@@ -718,19 +718,19 @@
     <xf numFmtId="41" fontId="0" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -743,19 +743,19 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="14" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="15" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="15" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="15" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="16" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="16" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -775,27 +775,27 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1931,7 +1931,7 @@
         <v>5224.3599999999997</v>
       </c>
       <c r="E34" s="39">
-        <v>0</v>
+        <v>7215472</v>
       </c>
       <c r="F34" s="40"/>
       <c r="G34" s="40"/>
@@ -2631,7 +2631,7 @@
         <v>6244.13</v>
       </c>
       <c r="E62" s="39">
-        <v>0</v>
+        <v>6907829</v>
       </c>
       <c r="F62" s="40"/>
       <c r="G62" s="40"/>
@@ -3406,7 +3406,7 @@
         <v>5052.46</v>
       </c>
       <c r="E93" s="39">
-        <v>0</v>
+        <v>7159542</v>
       </c>
       <c r="F93" s="40"/>
       <c r="G93" s="40"/>
@@ -4106,7 +4106,7 @@
         <v>6598.87</v>
       </c>
       <c r="E121" s="39">
-        <v>0</v>
+        <v>13471723</v>
       </c>
       <c r="F121" s="40"/>
       <c r="G121" s="40"/>
@@ -4756,7 +4756,7 @@
         <v>8476.15</v>
       </c>
       <c r="E147" s="39">
-        <v>0</v>
+        <v>14703327</v>
       </c>
       <c r="F147" s="40"/>
       <c r="G147" s="40"/>
@@ -4973,72 +4973,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="55">
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="50">
         <v>0.7</v>
       </c>
-      <c r="M1" s="49" t="s">
+      <c r="M1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="56"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="55">
+      <c r="N1" s="53"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="50">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="48"/>
+      <c r="Q1" s="52"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="49" t="s">
+      <c r="T1" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="48"/>
+      <c r="U1" s="52"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="54"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="57"/>
       <c r="G2" s="45"/>
       <c r="H2" s="45"/>
       <c r="I2" s="45"/>
       <c r="J2" s="45"/>
       <c r="K2" s="45"/>
-      <c r="L2" s="51"/>
+      <c r="L2" s="49"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="49" t="s">
+      <c r="O2" s="52"/>
+      <c r="P2" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="48"/>
+      <c r="Q2" s="52"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>26</v>
@@ -5051,31 +5051,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="54"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="57"/>
       <c r="G3" s="45"/>
       <c r="H3" s="45"/>
       <c r="I3" s="45"/>
       <c r="J3" s="45"/>
       <c r="K3" s="45"/>
-      <c r="L3" s="47">
+      <c r="L3" s="54">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="47">
+      <c r="N3" s="54">
         <v>14760</v>
       </c>
-      <c r="O3" s="48"/>
-      <c r="P3" s="47">
+      <c r="O3" s="52"/>
+      <c r="P3" s="54">
         <v>8125</v>
       </c>
-      <c r="Q3" s="48"/>
+      <c r="Q3" s="52"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>28</v>
@@ -5088,18 +5088,18 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="54"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
       <c r="G4" s="45"/>
       <c r="H4" s="45"/>
       <c r="I4" s="45"/>
       <c r="J4" s="45"/>
       <c r="K4" s="45"/>
-      <c r="L4" s="51"/>
+      <c r="L4" s="49"/>
       <c r="M4" s="2" t="s">
         <v>29</v>
       </c>
@@ -5107,10 +5107,10 @@
         <v>34705</v>
       </c>
       <c r="O4" s="59"/>
-      <c r="P4" s="47">
+      <c r="P4" s="54">
         <v>13230</v>
       </c>
-      <c r="Q4" s="48"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>30</v>
@@ -5548,16 +5548,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5565,6 +5555,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/_단기투자_INPUT.xlsx
+++ b/_단기투자_INPUT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF7B052-B1D4-4FE7-85EA-F8A56E39831F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3DA2A7-311B-441E-BB36-CE6EB7A76171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>📊  단기투자 일별 입력 시트  —  매일 맨 아래 행에 추가</t>
   </si>
@@ -91,9 +91,6 @@
   <si>
     <t>8번계좌
 잔고</t>
-  </si>
-  <si>
-    <t>← 여기에 날짜 입력</t>
   </si>
   <si>
     <t>코스피</t>
@@ -177,7 +174,7 @@
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="180" formatCode="\+#,##0;\-#,##0;0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -327,14 +324,6 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF94A3B8"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -402,7 +391,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -612,21 +601,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -639,7 +613,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -764,10 +738,6 @@
     <xf numFmtId="3" fontId="18" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -775,22 +745,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,6 +763,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1093,38 +1063,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="32" t="s">
@@ -4933,22 +4903,46 @@
         <v>7250270</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A154" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" s="43"/>
-      <c r="C154" s="43"/>
-      <c r="D154" s="43"/>
-      <c r="E154" s="43"/>
-      <c r="F154" s="43"/>
-      <c r="G154" s="43"/>
-      <c r="H154" s="43"/>
-      <c r="I154" s="43"/>
-      <c r="J154" s="43"/>
-      <c r="K154" s="43"/>
-      <c r="L154" s="43"/>
-      <c r="M154" s="43"/>
+    <row r="154" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A154" s="35">
+        <v>46183</v>
+      </c>
+      <c r="B154" s="36">
+        <v>137942555</v>
+      </c>
+      <c r="C154" s="37">
+        <v>10719350</v>
+      </c>
+      <c r="D154" s="38">
+        <v>7730.82</v>
+      </c>
+      <c r="E154" s="37">
+        <v>0</v>
+      </c>
+      <c r="F154" s="41">
+        <v>12127600</v>
+      </c>
+      <c r="G154" s="41">
+        <v>12434900</v>
+      </c>
+      <c r="H154" s="41">
+        <v>19299400</v>
+      </c>
+      <c r="I154" s="41">
+        <v>26302990</v>
+      </c>
+      <c r="J154" s="41">
+        <v>21467115</v>
+      </c>
+      <c r="K154" s="41">
+        <v>13204750</v>
+      </c>
+      <c r="L154" s="41">
+        <v>24122150</v>
+      </c>
+      <c r="M154" s="41">
+        <v>8983650</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4974,48 +4968,48 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="47" t="s">
+      <c r="D1" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="E1" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="F1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="55">
+        <v>0.7</v>
+      </c>
+      <c r="M1" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="50">
-        <v>0.7</v>
-      </c>
-      <c r="M1" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="53"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="50">
+      <c r="N1" s="56"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="55">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="52"/>
+      <c r="Q1" s="46"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T1" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" s="52"/>
+        <v>23</v>
+      </c>
+      <c r="U1" s="46"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2" s="48"/>
@@ -5023,25 +5017,25 @@
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
       <c r="E2" s="48"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
       <c r="L2" s="49"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="52"/>
+      <c r="N2" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="46"/>
       <c r="P2" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="52"/>
+        <v>24</v>
+      </c>
+      <c r="Q2" s="46"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T2" s="6">
         <v>0.8</v>
@@ -5056,29 +5050,29 @@
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
       <c r="E3" s="48"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="54">
+      <c r="F3" s="52"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="45">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="54">
+        <v>26</v>
+      </c>
+      <c r="N3" s="45">
         <v>14760</v>
       </c>
-      <c r="O3" s="52"/>
-      <c r="P3" s="54">
+      <c r="O3" s="46"/>
+      <c r="P3" s="45">
         <v>8125</v>
       </c>
-      <c r="Q3" s="52"/>
+      <c r="Q3" s="46"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T3" s="6">
         <v>0.75</v>
@@ -5093,27 +5087,27 @@
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
       <c r="L4" s="49"/>
       <c r="M4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="58">
+        <v>28</v>
+      </c>
+      <c r="N4" s="53">
         <v>34705</v>
       </c>
-      <c r="O4" s="59"/>
-      <c r="P4" s="54">
+      <c r="O4" s="54"/>
+      <c r="P4" s="45">
         <v>13230</v>
       </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="46"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T4" s="6">
         <v>0.7</v>
@@ -5124,7 +5118,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="10">
         <v>60000000</v>
@@ -5188,7 +5182,7 @@
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T5" s="6">
         <v>0.65</v>
@@ -5199,7 +5193,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="10">
         <v>10966894</v>
@@ -5263,7 +5257,7 @@
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T6" s="6">
         <v>0.6</v>
@@ -5274,7 +5268,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A7" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="10">
         <v>5712304</v>
@@ -5342,7 +5336,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A8" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="10">
         <v>10523398</v>
@@ -5411,7 +5405,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A9" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="10">
         <v>4348418</v>
@@ -5478,7 +5472,7 @@
     </row>
     <row r="10" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="25">
         <v>5368997</v>
@@ -5548,6 +5542,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5555,16 +5559,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/_단기투자_INPUT.xlsx
+++ b/_단기투자_INPUT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3DA2A7-311B-441E-BB36-CE6EB7A76171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DD6654-674F-4CC5-8CF5-7F2A8D1752B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,15 +745,22 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -763,13 +770,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -1052,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" style="31" customWidth="1"/>
@@ -4942,6 +4942,47 @@
       </c>
       <c r="M154" s="41">
         <v>8983650</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A155" s="35">
+        <v>46184</v>
+      </c>
+      <c r="B155" s="36">
+        <v>163915240</v>
+      </c>
+      <c r="C155" s="37">
+        <v>14395055</v>
+      </c>
+      <c r="D155" s="38">
+        <v>7763.95</v>
+      </c>
+      <c r="E155" s="37">
+        <v>0</v>
+      </c>
+      <c r="F155" s="41">
+        <v>12931670</v>
+      </c>
+      <c r="G155" s="41">
+        <v>12744060</v>
+      </c>
+      <c r="H155" s="41">
+        <v>20319260</v>
+      </c>
+      <c r="I155" s="41">
+        <v>27594910</v>
+      </c>
+      <c r="J155" s="41">
+        <v>29644530</v>
+      </c>
+      <c r="K155" s="41">
+        <v>23024190</v>
+      </c>
+      <c r="L155" s="41">
+        <v>27438530</v>
+      </c>
+      <c r="M155" s="41">
+        <v>10218090</v>
       </c>
     </row>
   </sheetData>
@@ -4967,72 +5008,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="55">
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="48">
         <v>0.7</v>
       </c>
-      <c r="M1" s="47" t="s">
+      <c r="M1" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="56"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="55">
+      <c r="N1" s="51"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="48">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="46"/>
+      <c r="Q1" s="50"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="47" t="s">
+      <c r="T1" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="46"/>
+      <c r="U1" s="50"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="52"/>
+      <c r="A2" s="46"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="55"/>
       <c r="G2" s="43"/>
       <c r="H2" s="43"/>
       <c r="I2" s="43"/>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
-      <c r="L2" s="49"/>
+      <c r="L2" s="47"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="55" t="s">
+      <c r="N2" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="46"/>
-      <c r="P2" s="47" t="s">
+      <c r="O2" s="50"/>
+      <c r="P2" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="46"/>
+      <c r="Q2" s="50"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5045,31 +5086,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="48"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="52"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="55"/>
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
       <c r="J3" s="43"/>
       <c r="K3" s="43"/>
-      <c r="L3" s="45">
+      <c r="L3" s="52">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="45">
+      <c r="N3" s="52">
         <v>14760</v>
       </c>
-      <c r="O3" s="46"/>
-      <c r="P3" s="45">
+      <c r="O3" s="50"/>
+      <c r="P3" s="52">
         <v>8125</v>
       </c>
-      <c r="Q3" s="46"/>
+      <c r="Q3" s="50"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5082,29 +5123,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="49"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="52"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="55"/>
       <c r="G4" s="43"/>
       <c r="H4" s="43"/>
       <c r="I4" s="43"/>
       <c r="J4" s="43"/>
       <c r="K4" s="43"/>
-      <c r="L4" s="49"/>
+      <c r="L4" s="47"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="53">
+      <c r="N4" s="56">
         <v>34705</v>
       </c>
-      <c r="O4" s="54"/>
-      <c r="P4" s="45">
+      <c r="O4" s="57"/>
+      <c r="P4" s="52">
         <v>13230</v>
       </c>
-      <c r="Q4" s="46"/>
+      <c r="Q4" s="50"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5542,16 +5583,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5559,6 +5590,16 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">

--- a/_단기투자_INPUT.xlsx
+++ b/_단기투자_INPUT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup01\Desktop\병아리\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DD6654-674F-4CC5-8CF5-7F2A8D1752B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED36F98B-7950-40A8-B9F5-0EDE48B0BEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,22 +745,15 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -770,6 +763,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -4958,7 +4958,7 @@
         <v>7763.95</v>
       </c>
       <c r="E155" s="37">
-        <v>0</v>
+        <v>1438756</v>
       </c>
       <c r="F155" s="41">
         <v>12931670</v>
@@ -5008,72 +5008,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="48">
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="55">
         <v>0.7</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="M1" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="51"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="48">
+      <c r="N1" s="56"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="55">
         <v>0.25</v>
       </c>
-      <c r="Q1" s="50"/>
+      <c r="Q1" s="46"/>
       <c r="R1" s="1"/>
       <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="45" t="s">
+      <c r="T1" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="50"/>
+      <c r="U1" s="46"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="55"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="52"/>
       <c r="G2" s="43"/>
       <c r="H2" s="43"/>
       <c r="I2" s="43"/>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
-      <c r="L2" s="47"/>
+      <c r="L2" s="49"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="50"/>
-      <c r="P2" s="45" t="s">
+      <c r="O2" s="46"/>
+      <c r="P2" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="50"/>
+      <c r="Q2" s="46"/>
       <c r="R2" s="1"/>
       <c r="S2" s="4" t="s">
         <v>25</v>
@@ -5086,31 +5086,31 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="55"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="52"/>
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
       <c r="J3" s="43"/>
       <c r="K3" s="43"/>
-      <c r="L3" s="52">
+      <c r="L3" s="45">
         <v>17485</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3" s="45">
         <v>14760</v>
       </c>
-      <c r="O3" s="50"/>
-      <c r="P3" s="52">
+      <c r="O3" s="46"/>
+      <c r="P3" s="45">
         <v>8125</v>
       </c>
-      <c r="Q3" s="50"/>
+      <c r="Q3" s="46"/>
       <c r="R3" s="1"/>
       <c r="S3" s="4" t="s">
         <v>27</v>
@@ -5123,29 +5123,29 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="55"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="52"/>
       <c r="G4" s="43"/>
       <c r="H4" s="43"/>
       <c r="I4" s="43"/>
       <c r="J4" s="43"/>
       <c r="K4" s="43"/>
-      <c r="L4" s="47"/>
+      <c r="L4" s="49"/>
       <c r="M4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="56">
+      <c r="N4" s="53">
         <v>34705</v>
       </c>
-      <c r="O4" s="57"/>
-      <c r="P4" s="52">
+      <c r="O4" s="54"/>
+      <c r="P4" s="45">
         <v>13230</v>
       </c>
-      <c r="Q4" s="50"/>
+      <c r="Q4" s="46"/>
       <c r="R4" s="1"/>
       <c r="S4" s="4" t="s">
         <v>29</v>
@@ -5583,6 +5583,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="N3:O3"/>
@@ -5590,16 +5600,6 @@
     <mergeCell ref="F1:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="E1:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E5:E10">
